--- a/data/raw/benv_exports/west_nile_fever_2026_italia.xlsx
+++ b/data/raw/benv_exports/west_nile_fever_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K76"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,217 +414,217 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>84069</v>
+        <v>85418</v>
       </c>
       <c r="B2" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
       </c>
       <c r="C2" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D2" t="str">
-        <v>14/04/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="E2" t="str">
-        <v>02/04/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>-</v>
+        <v>23/07/2026</v>
       </c>
       <c r="G2" t="str">
         <v>Lineage 2</v>
       </c>
       <c r="H2" t="str">
-        <v>CORNACCHIA</v>
+        <v>GAZZA</v>
       </c>
       <c r="I2" t="str">
-        <v>SAN VERO MILIS</v>
+        <v>VERBANIA</v>
       </c>
       <c r="J2" t="str">
-        <v>OR</v>
+        <v>VB</v>
       </c>
       <c r="K2" t="str">
-        <v>SARDEGNA</v>
+        <v>PIEMONTE</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>85373</v>
+        <v>85662</v>
       </c>
       <c r="B3" t="str">
-        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C3" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D3" t="str">
-        <v>03/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="E3" t="str">
-        <v>29/06/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>-</v>
+        <v>21/07/2026</v>
       </c>
       <c r="G3" t="str">
         <v>Lineage 2</v>
       </c>
       <c r="H3" t="str">
-        <v>INSETTI (VARIE SPECIE)</v>
+        <v>CORNACCHIA GRIGIA</v>
       </c>
       <c r="I3" t="str">
-        <v>CHIARI</v>
+        <v>ARGENTA</v>
       </c>
       <c r="J3" t="str">
-        <v>BS</v>
+        <v>FE</v>
       </c>
       <c r="K3" t="str">
-        <v>LOMBARDIA</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>85417</v>
+        <v>85578</v>
       </c>
       <c r="B4" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
       </c>
       <c r="C4" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D4" t="str">
-        <v>06/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="E4" t="str">
-        <v>20/06/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>-</v>
+        <v>16/07/2026</v>
       </c>
       <c r="G4" t="str">
         <v>Lineage 2</v>
       </c>
       <c r="H4" t="str">
-        <v>MERLO</v>
+        <v>INSETTI (VARIE SPECIE)</v>
       </c>
       <c r="I4" t="str">
-        <v>VERBANIA</v>
+        <v>CASTELVETRO PIACENTINO</v>
       </c>
       <c r="J4" t="str">
-        <v>VB</v>
+        <v>PC</v>
       </c>
       <c r="K4" t="str">
-        <v>PIEMONTE</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>84003</v>
+        <v>85650</v>
       </c>
       <c r="B5" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C5" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D5" t="str">
-        <v>03/04/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="E5" t="str">
-        <v>31/03/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="F5" t="str">
-        <v>-</v>
+        <v>16/07/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>Lineage 2</v>
+        <v>Lineage 1 e 2</v>
       </c>
       <c r="H5" t="str">
-        <v>CORNACCHIA GRIGIA</v>
+        <v>GAZZA</v>
       </c>
       <c r="I5" t="str">
-        <v>ORISTANO</v>
+        <v>ARGENTA</v>
       </c>
       <c r="J5" t="str">
-        <v>OR</v>
+        <v>FE</v>
       </c>
       <c r="K5" t="str">
-        <v>SARDEGNA</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>84069</v>
+        <v>85904</v>
       </c>
       <c r="B6" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C6" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D6" t="str">
-        <v>14/04/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>02/04/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="F6" t="str">
-        <v>-</v>
+        <v>28/07/2026</v>
       </c>
       <c r="G6" t="str">
         <v>Lineage 2</v>
       </c>
       <c r="H6" t="str">
-        <v>CORNACCHIA GRIGIA</v>
+        <v>GAZZA</v>
       </c>
       <c r="I6" t="str">
-        <v>SAN VERO MILIS</v>
+        <v>PORTOMAGGIORE</v>
       </c>
       <c r="J6" t="str">
-        <v>OR</v>
+        <v>FE</v>
       </c>
       <c r="K6" t="str">
-        <v>SARDEGNA</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>85407</v>
+        <v>85601</v>
       </c>
       <c r="B7" t="str">
-        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C7" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D7" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="E7" t="str">
         <v>06/07/2026</v>
       </c>
-      <c r="E7" t="str">
-        <v>01/07/2026</v>
-      </c>
       <c r="F7" t="str">
-        <v>-</v>
+        <v>13/07/2026</v>
       </c>
       <c r="G7" t="str">
         <v>Lineage 2</v>
       </c>
       <c r="H7" t="str">
-        <v>INSETTI (VARIE SPECIE)</v>
+        <v>GAZZA</v>
       </c>
       <c r="I7" t="str">
-        <v>TICINETO</v>
+        <v>FERRARA</v>
       </c>
       <c r="J7" t="str">
-        <v>AL</v>
+        <v>FE</v>
       </c>
       <c r="K7" t="str">
-        <v>PIEMONTE</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>85578</v>
+        <v>85352</v>
       </c>
       <c r="B8" t="str">
         <v>SORVEGLIANZA ENTOMOLOGICA</v>
@@ -633,46 +633,46 @@
         <v>C</v>
       </c>
       <c r="D8" t="str">
-        <v>08/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="E8" t="str">
-        <v>03/07/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="F8" t="str">
         <v>-</v>
       </c>
       <c r="G8" t="str">
-        <v>Lineage 2</v>
+        <v>Lineage 1</v>
       </c>
       <c r="H8" t="str">
         <v>INSETTI (VARIE SPECIE)</v>
       </c>
       <c r="I8" t="str">
-        <v>CASTELVETRO PIACENTINO</v>
+        <v>VILLAFRANCA DI VERONA</v>
       </c>
       <c r="J8" t="str">
-        <v>PC</v>
+        <v>VR</v>
       </c>
       <c r="K8" t="str">
-        <v>EMILIA ROMAGNA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>85476</v>
+        <v>85543</v>
       </c>
       <c r="B9" t="str">
-        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C9" t="str">
         <v>C</v>
       </c>
       <c r="D9" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="E9" t="str">
         <v>08/07/2026</v>
       </c>
-      <c r="E9" t="str">
-        <v>03/07/2026</v>
-      </c>
       <c r="F9" t="str">
         <v>-</v>
       </c>
@@ -680,13 +680,13 @@
         <v>Lineage 2</v>
       </c>
       <c r="H9" t="str">
-        <v>INSETTI (VARIE SPECIE)</v>
+        <v>GAZZA</v>
       </c>
       <c r="I9" t="str">
-        <v>MANTOVA</v>
+        <v>LODI</v>
       </c>
       <c r="J9" t="str">
-        <v>MN</v>
+        <v>LO</v>
       </c>
       <c r="K9" t="str">
         <v>LOMBARDIA</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>85310</v>
+        <v>85599</v>
       </c>
       <c r="B10" t="str">
         <v>SORVEGLIANZA ENTOMOLOGICA</v>
@@ -703,10 +703,10 @@
         <v>C</v>
       </c>
       <c r="D10" t="str">
-        <v>24/06/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>19/06/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="F10" t="str">
         <v>-</v>
@@ -718,53 +718,53 @@
         <v>INSETTI (VARIE SPECIE)</v>
       </c>
       <c r="I10" t="str">
-        <v>MESOLA</v>
+        <v>NOGAROLE ROCCA</v>
       </c>
       <c r="J10" t="str">
-        <v>FE</v>
+        <v>VR</v>
       </c>
       <c r="K10" t="str">
-        <v>EMILIA ROMAGNA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>85182</v>
+        <v>85373</v>
       </c>
       <c r="B11" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
       </c>
       <c r="C11" t="str">
         <v>C</v>
       </c>
       <c r="D11" t="str">
-        <v>24/06/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>18/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="F11" t="str">
         <v>-</v>
       </c>
       <c r="G11" t="str">
-        <v>Lineage 1</v>
+        <v>Lineage 2</v>
       </c>
       <c r="H11" t="str">
-        <v>GAZZA</v>
+        <v>INSETTI (VARIE SPECIE)</v>
       </c>
       <c r="I11" t="str">
-        <v>CASALEONE</v>
+        <v>CHIARI</v>
       </c>
       <c r="J11" t="str">
-        <v>VR</v>
+        <v>BS</v>
       </c>
       <c r="K11" t="str">
-        <v>VENETO</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>85298</v>
+        <v>85542</v>
       </c>
       <c r="B12" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -773,10 +773,10 @@
         <v>C</v>
       </c>
       <c r="D12" t="str">
-        <v>01/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="E12" t="str">
-        <v>13/06/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="F12" t="str">
         <v>-</v>
@@ -785,13 +785,13 @@
         <v>Lineage 2</v>
       </c>
       <c r="H12" t="str">
-        <v>CORVO</v>
+        <v>GAZZA</v>
       </c>
       <c r="I12" t="str">
-        <v>VELEZZO LOMELLINA</v>
+        <v>SEDRIANO</v>
       </c>
       <c r="J12" t="str">
-        <v>PV</v>
+        <v>MI</v>
       </c>
       <c r="K12" t="str">
         <v>LOMBARDIA</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>85328</v>
+        <v>85748</v>
       </c>
       <c r="B13" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -808,33 +808,33 @@
         <v>C</v>
       </c>
       <c r="D13" t="str">
-        <v>01/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="E13" t="str">
-        <v>26/06/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="F13" t="str">
         <v>-</v>
       </c>
       <c r="G13" t="str">
-        <v>Lineage 2</v>
+        <v>Lineage 1</v>
       </c>
       <c r="H13" t="str">
-        <v>GAZZA</v>
+        <v>CORNACCHIA GRIGIA</v>
       </c>
       <c r="I13" t="str">
-        <v>CAMPOMORONE</v>
+        <v>CREMONA</v>
       </c>
       <c r="J13" t="str">
-        <v>GE</v>
+        <v>CR</v>
       </c>
       <c r="K13" t="str">
-        <v>LIGURIA</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>84252</v>
+        <v>85816</v>
       </c>
       <c r="B14" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -843,80 +843,80 @@
         <v>C</v>
       </c>
       <c r="D14" t="str">
-        <v>20/04/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="E14" t="str">
-        <v>15/04/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="F14" t="str">
         <v>-</v>
       </c>
       <c r="G14" t="str">
-        <v>Lineage 1</v>
+        <v>Lineage 2</v>
       </c>
       <c r="H14" t="str">
-        <v>CORNACCHIA GRIGIA</v>
+        <v>GAZZA</v>
       </c>
       <c r="I14" t="str">
-        <v>CABRAS</v>
+        <v>CAPALBIO</v>
       </c>
       <c r="J14" t="str">
-        <v>OR</v>
+        <v>GR</v>
       </c>
       <c r="K14" t="str">
-        <v>SARDEGNA</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>85475</v>
+        <v>84069</v>
       </c>
       <c r="B15" t="str">
-        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C15" t="str">
         <v>C</v>
       </c>
       <c r="D15" t="str">
-        <v>08/07/2026</v>
+        <v>14/04/2026</v>
       </c>
       <c r="E15" t="str">
-        <v>03/07/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="F15" t="str">
         <v>-</v>
       </c>
       <c r="G15" t="str">
-        <v>Lineage 1</v>
+        <v>Lineage 2</v>
       </c>
       <c r="H15" t="str">
-        <v>INSETTI (VARIE SPECIE)</v>
+        <v>CORNACCHIA</v>
       </c>
       <c r="I15" t="str">
-        <v>MOTTEGGIANA</v>
+        <v>SAN VERO MILIS</v>
       </c>
       <c r="J15" t="str">
-        <v>MN</v>
+        <v>OR</v>
       </c>
       <c r="K15" t="str">
-        <v>LOMBARDIA</v>
+        <v>SARDEGNA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>85418</v>
+        <v>85229</v>
       </c>
       <c r="B16" t="str">
-        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C16" t="str">
         <v>C</v>
       </c>
       <c r="D16" t="str">
-        <v>06/07/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="E16" t="str">
-        <v>21/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="F16" t="str">
         <v>-</v>
@@ -925,21 +925,21 @@
         <v>Lineage 2</v>
       </c>
       <c r="H16" t="str">
-        <v>GAZZA</v>
+        <v>CORNACCHIA GRIGIA</v>
       </c>
       <c r="I16" t="str">
-        <v>VERBANIA</v>
+        <v>SARDARA</v>
       </c>
       <c r="J16" t="str">
-        <v>VB</v>
+        <v>SU</v>
       </c>
       <c r="K16" t="str">
-        <v>PIEMONTE</v>
+        <v>SARDEGNA</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>85352</v>
+        <v>85666</v>
       </c>
       <c r="B17" t="str">
         <v>SORVEGLIANZA ENTOMOLOGICA</v>
@@ -948,33 +948,33 @@
         <v>C</v>
       </c>
       <c r="D17" t="str">
-        <v>02/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="E17" t="str">
-        <v>26/06/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="F17" t="str">
         <v>-</v>
       </c>
       <c r="G17" t="str">
-        <v>Lineage 1</v>
+        <v>Lineage 2</v>
       </c>
       <c r="H17" t="str">
         <v>INSETTI (VARIE SPECIE)</v>
       </c>
       <c r="I17" t="str">
-        <v>VILLAFRANCA DI VERONA</v>
+        <v>MISANO ADRIATICO</v>
       </c>
       <c r="J17" t="str">
-        <v>VR</v>
+        <v>RN</v>
       </c>
       <c r="K17" t="str">
-        <v>VENETO</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>85229</v>
+        <v>84509</v>
       </c>
       <c r="B18" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -983,10 +983,10 @@
         <v>C</v>
       </c>
       <c r="D18" t="str">
-        <v>25/06/2026</v>
+        <v>07/05/2026</v>
       </c>
       <c r="E18" t="str">
-        <v>18/06/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="F18" t="str">
         <v>-</v>
@@ -995,21 +995,21 @@
         <v>Lineage 2</v>
       </c>
       <c r="H18" t="str">
-        <v>CORNACCHIA GRIGIA</v>
+        <v>AQUILA REALE</v>
       </c>
       <c r="I18" t="str">
-        <v>SARDARA</v>
+        <v>BARGE</v>
       </c>
       <c r="J18" t="str">
-        <v>SU</v>
+        <v>CN</v>
       </c>
       <c r="K18" t="str">
-        <v>SARDEGNA</v>
+        <v>PIEMONTE</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>84509</v>
+        <v>85694</v>
       </c>
       <c r="B19" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1018,33 +1018,2028 @@
         <v>C</v>
       </c>
       <c r="D19" t="str">
-        <v>07/05/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="E19" t="str">
-        <v>04/05/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="F19" t="str">
         <v>-</v>
       </c>
       <c r="G19" t="str">
-        <v>Lineage 2</v>
+        <v>Lineage 1</v>
       </c>
       <c r="H19" t="str">
-        <v>AQUILA REALE</v>
+        <v>GABBIANO REALE</v>
       </c>
       <c r="I19" t="str">
-        <v>BARGE</v>
+        <v>PAGAZZANO</v>
       </c>
       <c r="J19" t="str">
-        <v>CN</v>
+        <v>BG</v>
       </c>
       <c r="K19" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>85902</v>
+      </c>
+      <c r="B20" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C20" t="str">
+        <v>C</v>
+      </c>
+      <c r="D20" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="E20" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="F20" t="str">
+        <v>-</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H20" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I20" t="str">
+        <v>FABBRICO</v>
+      </c>
+      <c r="J20" t="str">
+        <v>RE</v>
+      </c>
+      <c r="K20" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>85905</v>
+      </c>
+      <c r="B21" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C21" t="str">
+        <v>C</v>
+      </c>
+      <c r="D21" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="E21" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="F21" t="str">
+        <v>-</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Lineage 1 e 2</v>
+      </c>
+      <c r="H21" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I21" t="str">
+        <v>OSTELLATO</v>
+      </c>
+      <c r="J21" t="str">
+        <v>FE</v>
+      </c>
+      <c r="K21" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>85566</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C22" t="str">
+        <v>C</v>
+      </c>
+      <c r="D22" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E22" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F22" t="str">
+        <v>-</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H22" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I22" t="str">
+        <v>BARBARANO MOSSANO</v>
+      </c>
+      <c r="J22" t="str">
+        <v>VI</v>
+      </c>
+      <c r="K22" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>85602</v>
+      </c>
+      <c r="B23" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C23" t="str">
+        <v>C</v>
+      </c>
+      <c r="D23" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="E23" t="str">
+        <v>07/07/2026</v>
+      </c>
+      <c r="F23" t="str">
+        <v>-</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H23" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I23" t="str">
+        <v>COLORNO</v>
+      </c>
+      <c r="J23" t="str">
+        <v>PR</v>
+      </c>
+      <c r="K23" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>85693</v>
+      </c>
+      <c r="B24" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C24" t="str">
+        <v>C</v>
+      </c>
+      <c r="D24" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E24" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="F24" t="str">
+        <v>-</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H24" t="str">
+        <v>AIRONE CENERINO</v>
+      </c>
+      <c r="I24" t="str">
+        <v>SORISOLE</v>
+      </c>
+      <c r="J24" t="str">
+        <v>BG</v>
+      </c>
+      <c r="K24" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>85417</v>
+      </c>
+      <c r="B25" t="str">
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+      </c>
+      <c r="C25" t="str">
+        <v>C</v>
+      </c>
+      <c r="D25" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="E25" t="str">
+        <v>20/06/2026</v>
+      </c>
+      <c r="F25" t="str">
+        <v>-</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H25" t="str">
+        <v>MERLO</v>
+      </c>
+      <c r="I25" t="str">
+        <v>VERBANIA</v>
+      </c>
+      <c r="J25" t="str">
+        <v>VB</v>
+      </c>
+      <c r="K25" t="str">
+        <v>PIEMONTE</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>85628</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C26" t="str">
+        <v>C</v>
+      </c>
+      <c r="D26" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="E26" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="F26" t="str">
+        <v>-</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H26" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I26" t="str">
+        <v>VERCELLI</v>
+      </c>
+      <c r="J26" t="str">
+        <v>VC</v>
+      </c>
+      <c r="K26" t="str">
+        <v>PIEMONTE</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>85661</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C27" t="str">
+        <v>C</v>
+      </c>
+      <c r="D27" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="E27" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="F27" t="str">
+        <v>-</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H27" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I27" t="str">
+        <v>MEDICINA</v>
+      </c>
+      <c r="J27" t="str">
+        <v>BO</v>
+      </c>
+      <c r="K27" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>85899</v>
+      </c>
+      <c r="B28" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C28" t="str">
+        <v>C</v>
+      </c>
+      <c r="D28" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="E28" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="F28" t="str">
+        <v>-</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H28" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I28" t="str">
+        <v>CORREGGIO</v>
+      </c>
+      <c r="J28" t="str">
+        <v>RE</v>
+      </c>
+      <c r="K28" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>85900</v>
+      </c>
+      <c r="B29" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C29" t="str">
+        <v>C</v>
+      </c>
+      <c r="D29" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="E29" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="F29" t="str">
+        <v>-</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H29" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I29" t="str">
+        <v>POLESINE ZIBELLO</v>
+      </c>
+      <c r="J29" t="str">
+        <v>PR</v>
+      </c>
+      <c r="K29" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>84003</v>
+      </c>
+      <c r="B30" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C30" t="str">
+        <v>C</v>
+      </c>
+      <c r="D30" t="str">
+        <v>03/04/2026</v>
+      </c>
+      <c r="E30" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="F30" t="str">
+        <v>-</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H30" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I30" t="str">
+        <v>ORISTANO</v>
+      </c>
+      <c r="J30" t="str">
+        <v>OR</v>
+      </c>
+      <c r="K30" t="str">
+        <v>SARDEGNA</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>85511</v>
+      </c>
+      <c r="B31" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C31" t="str">
+        <v>C</v>
+      </c>
+      <c r="D31" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="E31" t="str">
+        <v>07/07/2026</v>
+      </c>
+      <c r="F31" t="str">
+        <v>-</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H31" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I31" t="str">
+        <v>CASALE MONFERRATO</v>
+      </c>
+      <c r="J31" t="str">
+        <v>AL</v>
+      </c>
+      <c r="K31" t="str">
+        <v>PIEMONTE</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>85620</v>
+      </c>
+      <c r="B32" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C32" t="str">
+        <v>C</v>
+      </c>
+      <c r="D32" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="E32" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F32" t="str">
+        <v>-</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H32" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I32" t="str">
+        <v>VILLACHIARA</v>
+      </c>
+      <c r="J32" t="str">
+        <v>BS</v>
+      </c>
+      <c r="K32" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>85627</v>
+      </c>
+      <c r="B33" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C33" t="str">
+        <v>C</v>
+      </c>
+      <c r="D33" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="E33" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="F33" t="str">
+        <v>-</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H33" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I33" t="str">
+        <v>TICINETO</v>
+      </c>
+      <c r="J33" t="str">
+        <v>AL</v>
+      </c>
+      <c r="K33" t="str">
+        <v>PIEMONTE</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>85598</v>
+      </c>
+      <c r="B34" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C34" t="str">
+        <v>C</v>
+      </c>
+      <c r="D34" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E34" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F34" t="str">
+        <v>-</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H34" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I34" t="str">
+        <v>QUARTO D\'ALTINO</v>
+      </c>
+      <c r="J34" t="str">
+        <v>VE</v>
+      </c>
+      <c r="K34" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>85624</v>
+      </c>
+      <c r="B35" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C35" t="str">
+        <v>C</v>
+      </c>
+      <c r="D35" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="E35" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="F35" t="str">
+        <v>-</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H35" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I35" t="str">
+        <v>CASALEONE</v>
+      </c>
+      <c r="J35" t="str">
+        <v>VR</v>
+      </c>
+      <c r="K35" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>85667</v>
+      </c>
+      <c r="B36" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C36" t="str">
+        <v>C</v>
+      </c>
+      <c r="D36" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="E36" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="F36" t="str">
+        <v>-</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H36" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I36" t="str">
+        <v>SAN CESARIO SUL PANARO</v>
+      </c>
+      <c r="J36" t="str">
+        <v>MO</v>
+      </c>
+      <c r="K36" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>85672</v>
+      </c>
+      <c r="B37" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C37" t="str">
+        <v>C</v>
+      </c>
+      <c r="D37" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E37" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="F37" t="str">
+        <v>-</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H37" t="str">
+        <v>COLOMBACCIO</v>
+      </c>
+      <c r="I37" t="str">
+        <v>PIEVE D\'OLMI</v>
+      </c>
+      <c r="J37" t="str">
+        <v>CR</v>
+      </c>
+      <c r="K37" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>85847</v>
+      </c>
+      <c r="B38" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C38" t="str">
+        <v>C</v>
+      </c>
+      <c r="D38" t="str">
+        <v>24/07/2026</v>
+      </c>
+      <c r="E38" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="F38" t="str">
+        <v>-</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H38" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I38" t="str">
+        <v>SABAUDIA</v>
+      </c>
+      <c r="J38" t="str">
+        <v>LT</v>
+      </c>
+      <c r="K38" t="str">
+        <v>LAZIO</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>84069</v>
+      </c>
+      <c r="B39" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C39" t="str">
+        <v>C</v>
+      </c>
+      <c r="D39" t="str">
+        <v>14/04/2026</v>
+      </c>
+      <c r="E39" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="F39" t="str">
+        <v>-</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H39" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I39" t="str">
+        <v>SAN VERO MILIS</v>
+      </c>
+      <c r="J39" t="str">
+        <v>OR</v>
+      </c>
+      <c r="K39" t="str">
+        <v>SARDEGNA</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>85541</v>
+      </c>
+      <c r="B40" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C40" t="str">
+        <v>C</v>
+      </c>
+      <c r="D40" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="E40" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="F40" t="str">
+        <v>-</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H40" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I40" t="str">
+        <v>POZZUOLO MARTESANA</v>
+      </c>
+      <c r="J40" t="str">
+        <v>MI</v>
+      </c>
+      <c r="K40" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>85660</v>
+      </c>
+      <c r="B41" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C41" t="str">
+        <v>C</v>
+      </c>
+      <c r="D41" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="E41" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F41" t="str">
+        <v>-</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Lineage 1 e 2</v>
+      </c>
+      <c r="H41" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>SORBOLO MEZZANI</v>
+      </c>
+      <c r="J41" t="str">
+        <v>PR</v>
+      </c>
+      <c r="K41" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>85671</v>
+      </c>
+      <c r="B42" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C42" t="str">
+        <v>C</v>
+      </c>
+      <c r="D42" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E42" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="F42" t="str">
+        <v>-</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H42" t="str">
+        <v>GABBIANO REALE</v>
+      </c>
+      <c r="I42" t="str">
+        <v>SIRMIONE</v>
+      </c>
+      <c r="J42" t="str">
+        <v>BS</v>
+      </c>
+      <c r="K42" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>85407</v>
+      </c>
+      <c r="B43" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C43" t="str">
+        <v>C</v>
+      </c>
+      <c r="D43" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="E43" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="F43" t="str">
+        <v>-</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H43" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>TICINETO</v>
+      </c>
+      <c r="J43" t="str">
+        <v>AL</v>
+      </c>
+      <c r="K43" t="str">
+        <v>PIEMONTE</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>85570</v>
+      </c>
+      <c r="B44" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C44" t="str">
+        <v>C</v>
+      </c>
+      <c r="D44" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E44" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F44" t="str">
+        <v>-</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H44" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I44" t="str">
+        <v>VILLANOVA DEL GHEBBO</v>
+      </c>
+      <c r="J44" t="str">
+        <v>RO</v>
+      </c>
+      <c r="K44" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>85571</v>
+      </c>
+      <c r="B45" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C45" t="str">
+        <v>C</v>
+      </c>
+      <c r="D45" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E45" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F45" t="str">
+        <v>-</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H45" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I45" t="str">
+        <v>BRUGINE</v>
+      </c>
+      <c r="J45" t="str">
+        <v>PD</v>
+      </c>
+      <c r="K45" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>85573</v>
+      </c>
+      <c r="B46" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C46" t="str">
+        <v>C</v>
+      </c>
+      <c r="D46" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="E46" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F46" t="str">
+        <v>-</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H46" t="str">
+        <v>MERLO</v>
+      </c>
+      <c r="I46" t="str">
+        <v>SESTO ED UNITI</v>
+      </c>
+      <c r="J46" t="str">
+        <v>CR</v>
+      </c>
+      <c r="K46" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>85574</v>
+      </c>
+      <c r="B47" t="str">
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+      </c>
+      <c r="C47" t="str">
+        <v>C</v>
+      </c>
+      <c r="D47" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="E47" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F47" t="str">
+        <v>-</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H47" t="str">
+        <v>MERLO</v>
+      </c>
+      <c r="I47" t="str">
+        <v>ROBECCO D\'OGLIO</v>
+      </c>
+      <c r="J47" t="str">
+        <v>CR</v>
+      </c>
+      <c r="K47" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>85585</v>
+      </c>
+      <c r="B48" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C48" t="str">
+        <v>C</v>
+      </c>
+      <c r="D48" t="str">
+        <v>21/07/2026</v>
+      </c>
+      <c r="E48" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="F48" t="str">
+        <v>-</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Lineage non determinato</v>
+      </c>
+      <c r="H48" t="str">
+        <v>CAVALLO</v>
+      </c>
+      <c r="I48" t="str">
+        <v>BORGO VENETO</v>
+      </c>
+      <c r="J48" t="str">
+        <v>PD</v>
+      </c>
+      <c r="K48" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>85665</v>
+      </c>
+      <c r="B49" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C49" t="str">
+        <v>C</v>
+      </c>
+      <c r="D49" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="E49" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="F49" t="str">
+        <v>-</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H49" t="str">
+        <v>CORNACCHIA NERA</v>
+      </c>
+      <c r="I49" t="str">
+        <v>CASTELVETRO PIACENTINO</v>
+      </c>
+      <c r="J49" t="str">
+        <v>PC</v>
+      </c>
+      <c r="K49" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>85675</v>
+      </c>
+      <c r="B50" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C50" t="str">
+        <v>C</v>
+      </c>
+      <c r="D50" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E50" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="F50" t="str">
+        <v>-</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Lineage 1 e 2</v>
+      </c>
+      <c r="H50" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I50" t="str">
+        <v>CURTATONE</v>
+      </c>
+      <c r="J50" t="str">
+        <v>MN</v>
+      </c>
+      <c r="K50" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>85476</v>
+      </c>
+      <c r="B51" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C51" t="str">
+        <v>C</v>
+      </c>
+      <c r="D51" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="E51" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="F51" t="str">
+        <v>-</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H51" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I51" t="str">
+        <v>MANTOVA</v>
+      </c>
+      <c r="J51" t="str">
+        <v>MN</v>
+      </c>
+      <c r="K51" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>85310</v>
+      </c>
+      <c r="B52" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C52" t="str">
+        <v>C</v>
+      </c>
+      <c r="D52" t="str">
+        <v>24/06/2026</v>
+      </c>
+      <c r="E52" t="str">
+        <v>19/06/2026</v>
+      </c>
+      <c r="F52" t="str">
+        <v>-</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H52" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I52" t="str">
+        <v>MESOLA</v>
+      </c>
+      <c r="J52" t="str">
+        <v>FE</v>
+      </c>
+      <c r="K52" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>85613</v>
+      </c>
+      <c r="B53" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C53" t="str">
+        <v>C</v>
+      </c>
+      <c r="D53" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E53" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="F53" t="str">
+        <v>-</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H53" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I53" t="str">
+        <v>CEREA</v>
+      </c>
+      <c r="J53" t="str">
+        <v>VR</v>
+      </c>
+      <c r="K53" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>85629</v>
+      </c>
+      <c r="B54" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C54" t="str">
+        <v>C</v>
+      </c>
+      <c r="D54" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="E54" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="F54" t="str">
+        <v>-</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H54" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I54" t="str">
+        <v>REFRANCORE</v>
+      </c>
+      <c r="J54" t="str">
+        <v>AT</v>
+      </c>
+      <c r="K54" t="str">
+        <v>PIEMONTE</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>85819</v>
+      </c>
+      <c r="B55" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C55" t="str">
+        <v>C</v>
+      </c>
+      <c r="D55" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="E55" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="F55" t="str">
+        <v>-</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H55" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I55" t="str">
+        <v>MOSCIANO SANT\'ANGELO</v>
+      </c>
+      <c r="J55" t="str">
+        <v>TE</v>
+      </c>
+      <c r="K55" t="str">
+        <v>ABRUZZO</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>85457</v>
+      </c>
+      <c r="B56" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C56" t="str">
+        <v>C</v>
+      </c>
+      <c r="D56" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="E56" t="str">
+        <v>02/07/2026</v>
+      </c>
+      <c r="F56" t="str">
+        <v>-</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H56" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I56" t="str">
+        <v>PADOVA</v>
+      </c>
+      <c r="J56" t="str">
+        <v>PD</v>
+      </c>
+      <c r="K56" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>85182</v>
+      </c>
+      <c r="B57" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C57" t="str">
+        <v>C</v>
+      </c>
+      <c r="D57" t="str">
+        <v>24/06/2026</v>
+      </c>
+      <c r="E57" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="F57" t="str">
+        <v>-</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H57" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I57" t="str">
+        <v>CASALEONE</v>
+      </c>
+      <c r="J57" t="str">
+        <v>VR</v>
+      </c>
+      <c r="K57" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>85606</v>
+      </c>
+      <c r="B58" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C58" t="str">
+        <v>C</v>
+      </c>
+      <c r="D58" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="E58" t="str">
+        <v>07/07/2026</v>
+      </c>
+      <c r="F58" t="str">
+        <v>-</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H58" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I58" t="str">
+        <v>FERRARA</v>
+      </c>
+      <c r="J58" t="str">
+        <v>FE</v>
+      </c>
+      <c r="K58" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>85636</v>
+      </c>
+      <c r="B59" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C59" t="str">
+        <v>C</v>
+      </c>
+      <c r="D59" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E59" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="F59" t="str">
+        <v>-</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H59" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I59" t="str">
+        <v>ROMA</v>
+      </c>
+      <c r="J59" t="str">
+        <v>RM</v>
+      </c>
+      <c r="K59" t="str">
+        <v>LAZIO</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>85637</v>
+      </c>
+      <c r="B60" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C60" t="str">
+        <v>C</v>
+      </c>
+      <c r="D60" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="E60" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="F60" t="str">
+        <v>-</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Lineage non determinato</v>
+      </c>
+      <c r="H60" t="str">
+        <v>CAVALLO</v>
+      </c>
+      <c r="I60" t="str">
+        <v>SAN GREGORIO DA SASSOLA</v>
+      </c>
+      <c r="J60" t="str">
+        <v>RM</v>
+      </c>
+      <c r="K60" t="str">
+        <v>LAZIO</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>85670</v>
+      </c>
+      <c r="B61" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C61" t="str">
+        <v>C</v>
+      </c>
+      <c r="D61" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E61" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="F61" t="str">
+        <v>-</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H61" t="str">
+        <v>GHEPPIO</v>
+      </c>
+      <c r="I61" t="str">
+        <v>LONATO DEL GARDA</v>
+      </c>
+      <c r="J61" t="str">
+        <v>BS</v>
+      </c>
+      <c r="K61" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>85603</v>
+      </c>
+      <c r="B62" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C62" t="str">
+        <v>C</v>
+      </c>
+      <c r="D62" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="E62" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="F62" t="str">
+        <v>-</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H62" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I62" t="str">
+        <v>BRESCELLO</v>
+      </c>
+      <c r="J62" t="str">
+        <v>RE</v>
+      </c>
+      <c r="K62" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>85710</v>
+      </c>
+      <c r="B63" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C63" t="str">
+        <v>C</v>
+      </c>
+      <c r="D63" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E63" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="F63" t="str">
+        <v>-</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H63" t="str">
+        <v>GHEPPIO</v>
+      </c>
+      <c r="I63" t="str">
+        <v>CARMIGNANO DI BRENTA</v>
+      </c>
+      <c r="J63" t="str">
+        <v>PD</v>
+      </c>
+      <c r="K63" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>85286</v>
+      </c>
+      <c r="B64" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C64" t="str">
+        <v>C</v>
+      </c>
+      <c r="D64" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="E64" t="str">
+        <v>24/06/2026</v>
+      </c>
+      <c r="F64" t="str">
+        <v>-</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Lineage non determinato</v>
+      </c>
+      <c r="H64" t="str">
+        <v>CAVALLO</v>
+      </c>
+      <c r="I64" t="str">
+        <v>NOTO</v>
+      </c>
+      <c r="J64" t="str">
+        <v>SR</v>
+      </c>
+      <c r="K64" t="str">
+        <v>SICILIA</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>85298</v>
+      </c>
+      <c r="B65" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C65" t="str">
+        <v>C</v>
+      </c>
+      <c r="D65" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="E65" t="str">
+        <v>13/06/2026</v>
+      </c>
+      <c r="F65" t="str">
+        <v>-</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H65" t="str">
+        <v>CORVO</v>
+      </c>
+      <c r="I65" t="str">
+        <v>VELEZZO LOMELLINA</v>
+      </c>
+      <c r="J65" t="str">
+        <v>PV</v>
+      </c>
+      <c r="K65" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>85328</v>
+      </c>
+      <c r="B66" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C66" t="str">
+        <v>C</v>
+      </c>
+      <c r="D66" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="E66" t="str">
+        <v>26/06/2026</v>
+      </c>
+      <c r="F66" t="str">
+        <v>-</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H66" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I66" t="str">
+        <v>CAMPOMORONE</v>
+      </c>
+      <c r="J66" t="str">
+        <v>GE</v>
+      </c>
+      <c r="K66" t="str">
+        <v>LIGURIA</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>85569</v>
+      </c>
+      <c r="B67" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C67" t="str">
+        <v>C</v>
+      </c>
+      <c r="D67" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="E67" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="F67" t="str">
+        <v>-</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H67" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I67" t="str">
+        <v>FICAROLO</v>
+      </c>
+      <c r="J67" t="str">
+        <v>RO</v>
+      </c>
+      <c r="K67" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>85711</v>
+      </c>
+      <c r="B68" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C68" t="str">
+        <v>C</v>
+      </c>
+      <c r="D68" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E68" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="F68" t="str">
+        <v>-</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H68" t="str">
+        <v>GABBIANO REALE</v>
+      </c>
+      <c r="I68" t="str">
+        <v>SCORZE\'</v>
+      </c>
+      <c r="J68" t="str">
+        <v>VE</v>
+      </c>
+      <c r="K68" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>85812</v>
+      </c>
+      <c r="B69" t="str">
+        <v>RISCONTRO ANATOMO-PATOLOGICO</v>
+      </c>
+      <c r="C69" t="str">
+        <v>C</v>
+      </c>
+      <c r="D69" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="E69" t="str">
+        <v>21/06/2026</v>
+      </c>
+      <c r="F69" t="str">
+        <v>-</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H69" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I69" t="str">
+        <v>VERBANIA</v>
+      </c>
+      <c r="J69" t="str">
+        <v>VB</v>
+      </c>
+      <c r="K69" t="str">
+        <v>PIEMONTE</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>84252</v>
+      </c>
+      <c r="B70" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C70" t="str">
+        <v>C</v>
+      </c>
+      <c r="D70" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="E70" t="str">
+        <v>15/04/2026</v>
+      </c>
+      <c r="F70" t="str">
+        <v>-</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H70" t="str">
+        <v>CORNACCHIA GRIGIA</v>
+      </c>
+      <c r="I70" t="str">
+        <v>CABRAS</v>
+      </c>
+      <c r="J70" t="str">
+        <v>OR</v>
+      </c>
+      <c r="K70" t="str">
+        <v>SARDEGNA</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>85475</v>
+      </c>
+      <c r="B71" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C71" t="str">
+        <v>C</v>
+      </c>
+      <c r="D71" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="E71" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="F71" t="str">
+        <v>-</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H71" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I71" t="str">
+        <v>MOTTEGGIANA</v>
+      </c>
+      <c r="J71" t="str">
+        <v>MN</v>
+      </c>
+      <c r="K71" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>85647</v>
+      </c>
+      <c r="B72" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C72" t="str">
+        <v>C</v>
+      </c>
+      <c r="D72" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E72" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="F72" t="str">
+        <v>-</v>
+      </c>
+      <c r="G72" t="str">
+        <v>Lineage 1 e 2</v>
+      </c>
+      <c r="H72" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I72" t="str">
+        <v>CASELLE LANDI</v>
+      </c>
+      <c r="J72" t="str">
+        <v>LO</v>
+      </c>
+      <c r="K72" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>85664</v>
+      </c>
+      <c r="B73" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C73" t="str">
+        <v>C</v>
+      </c>
+      <c r="D73" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="E73" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="F73" t="str">
+        <v>-</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H73" t="str">
+        <v>GAZZA</v>
+      </c>
+      <c r="I73" t="str">
+        <v>SAN SECONDO PARMENSE</v>
+      </c>
+      <c r="J73" t="str">
+        <v>PR</v>
+      </c>
+      <c r="K73" t="str">
+        <v>EMILIA ROMAGNA</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>85712</v>
+      </c>
+      <c r="B74" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C74" t="str">
+        <v>C</v>
+      </c>
+      <c r="D74" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="E74" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="F74" t="str">
+        <v>-</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H74" t="str">
+        <v>STROLAGA MEZZANA</v>
+      </c>
+      <c r="I74" t="str">
+        <v>VENEZIA</v>
+      </c>
+      <c r="J74" t="str">
+        <v>VE</v>
+      </c>
+      <c r="K74" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>85641</v>
+      </c>
+      <c r="B75" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C75" t="str">
+        <v>C</v>
+      </c>
+      <c r="D75" t="str">
+        <v>20/07/2026</v>
+      </c>
+      <c r="E75" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="F75" t="str">
+        <v>-</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Lineage 1</v>
+      </c>
+      <c r="H75" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I75" t="str">
+        <v>ORISTANO</v>
+      </c>
+      <c r="J75" t="str">
+        <v>OR</v>
+      </c>
+      <c r="K75" t="str">
+        <v>SARDEGNA</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>85408</v>
+      </c>
+      <c r="B76" t="str">
+        <v>SORVEGLIANZA ENTOMOLOGICA</v>
+      </c>
+      <c r="C76" t="str">
+        <v>C</v>
+      </c>
+      <c r="D76" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="E76" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="F76" t="str">
+        <v>-</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Lineage 2</v>
+      </c>
+      <c r="H76" t="str">
+        <v>INSETTI (VARIE SPECIE)</v>
+      </c>
+      <c r="I76" t="str">
+        <v>VESPOLATE</v>
+      </c>
+      <c r="J76" t="str">
+        <v>NO</v>
+      </c>
+      <c r="K76" t="str">
         <v>PIEMONTE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K76"/>
   </ignoredErrors>
 </worksheet>
 </file>